--- a/Day10/matrixes.xlsx
+++ b/Day10/matrixes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e03748fe74b2749e/Projetos/AdventOfCode2025/AdventOfCode2025/Day10/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="807" documentId="8_{804FC923-46C6-45E0-983F-7CE295EDADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{885717BE-6FC7-4BDE-BD1C-7D6C5A0064BD}"/>
+  <xr:revisionPtr revIDLastSave="1013" documentId="8_{804FC923-46C6-45E0-983F-7CE295EDADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D8F45AE-9725-4DA9-AF1F-13949E4F5E97}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E1441335-4A8F-4FC7-82E1-14FF11680EDB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E1441335-4A8F-4FC7-82E1-14FF11680EDB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
     <t>x5</t>
   </si>
   <si>
-    <t>Ñ</t>
+    <t>t</t>
   </si>
 </sst>
 </file>
@@ -192,7 +192,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -209,9 +209,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -224,10 +221,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -580,14 +577,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
       <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
@@ -737,13 +734,13 @@
     <row r="7" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
       <c r="G9" s="1" t="s">
         <v>14</v>
       </c>
@@ -904,12 +901,12 @@
       <c r="AS16" s="2"/>
     </row>
     <row r="17" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
       <c r="F17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1599,7 +1596,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C764131-1371-4089-ABCA-50D9E6D68031}">
-  <dimension ref="A1:AO496"/>
+  <dimension ref="B1:AO496"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="36" width="4.28515625" customWidth="1"/>
@@ -1609,18 +1606,15 @@
     <col min="42" max="89" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
       <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
@@ -1634,7 +1628,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1">
         <v>0</v>
       </c>
@@ -1678,20 +1672,17 @@
         <v>1</v>
       </c>
       <c r="U2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="1" cm="1">
-        <f t="array" ref="W2:W5">MMULT(N2:S5,U2:U7)</f>
-        <v>0</v>
+        <f t="array" ref="W2:W7">MMULT(N2:S7,U2:U7)</f>
+        <v>3</v>
       </c>
       <c r="Y2" s="1">
         <v>3</v>
       </c>
-      <c r="AA2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>0</v>
       </c>
@@ -1735,19 +1726,16 @@
         <v>1</v>
       </c>
       <c r="U3" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W3" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y3" s="1">
         <v>5</v>
       </c>
-      <c r="AA3" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>0</v>
       </c>
@@ -1800,16 +1788,13 @@
         <v>0</v>
       </c>
       <c r="W4" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="1">
         <v>4</v>
       </c>
-      <c r="AA4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1853,19 +1838,16 @@
         <v>0</v>
       </c>
       <c r="U5" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W5" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y5" s="1">
         <v>7</v>
       </c>
-      <c r="AA5" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
@@ -1900,22 +1882,22 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="1">
+        <v>1</v>
+      </c>
+      <c r="W6" s="1">
         <v>0</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
       </c>
-      <c r="AA6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1935,28 +1917,28 @@
         <v>0</v>
       </c>
       <c r="S7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="Y7" s="1">
         <v>0</v>
       </c>
-      <c r="AA7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <f>MDETERM(B10:G15)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AO9" s="3"/>
     </row>
-    <row r="10" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>0</v>
       </c>
@@ -1973,11 +1955,53 @@
         <v>1</v>
       </c>
       <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1">
         <v>3</v>
       </c>
+      <c r="Q10" s="1">
+        <v>1</v>
+      </c>
+      <c r="R10" s="1">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <v>1</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1">
+        <v>7</v>
+      </c>
       <c r="AO10" s="3"/>
     </row>
-    <row r="11" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>0</v>
       </c>
@@ -1994,10 +2018,52 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1">
+        <v>1</v>
+      </c>
+      <c r="W11" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>0</v>
       </c>
@@ -2014,10 +2080,52 @@
         <v>1</v>
       </c>
       <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1</v>
+      </c>
+      <c r="T12" s="1">
+        <v>1</v>
+      </c>
+      <c r="U12" s="1">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>1</v>
       </c>
@@ -2034,10 +2142,52 @@
         <v>0</v>
       </c>
       <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0</v>
+      </c>
+      <c r="U13" s="1">
+        <v>1</v>
+      </c>
+      <c r="V13" s="1">
+        <v>1</v>
+      </c>
+      <c r="W13" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>0</v>
       </c>
@@ -2051,13 +2201,55 @@
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>0</v>
       </c>
@@ -2076,26 +2268,236 @@
       <c r="G15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="J18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4</v>
+      </c>
+      <c r="J19" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1">
+        <v>3</v>
+      </c>
+      <c r="L20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="M20" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="U24" s="5"/>
     </row>
-    <row r="25" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="21:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2586,18 +2988,18 @@
     <col min="1" max="36" width="4.28515625" customWidth="1"/>
     <col min="37" max="37" width="4.42578125" customWidth="1"/>
     <col min="38" max="40" width="4.28515625" customWidth="1"/>
-    <col min="41" max="41" width="13" style="8" customWidth="1"/>
+    <col min="41" max="41" width="13" style="7" customWidth="1"/>
     <col min="42" max="89" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
       <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
@@ -2951,7 +3353,7 @@
         <v>7</v>
       </c>
       <c r="AN8" s="2"/>
-      <c r="AO8" s="7"/>
+      <c r="AO8" s="6"/>
       <c r="AP8" s="2"/>
       <c r="AQ8" s="2"/>
       <c r="AR8" s="2"/>
@@ -2980,7 +3382,7 @@
       <c r="Q9" s="1">
         <v>5</v>
       </c>
-      <c r="S9" s="10">
+      <c r="S9" s="9">
         <v>0</v>
       </c>
       <c r="T9" s="1">
@@ -2998,22 +3400,22 @@
       <c r="X9" s="1">
         <v>5</v>
       </c>
-      <c r="Z9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="10">
+      <c r="Z9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="9">
         <v>-1</v>
       </c>
-      <c r="AC9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="10">
+      <c r="AC9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="9">
         <v>5</v>
       </c>
       <c r="AG9" s="1">
@@ -3035,7 +3437,7 @@
         <v>5</v>
       </c>
       <c r="AN9" s="2"/>
-      <c r="AO9" s="7"/>
+      <c r="AO9" s="6"/>
       <c r="AP9" s="2"/>
       <c r="AQ9" s="2"/>
       <c r="AR9" s="2"/>
@@ -3060,7 +3462,7 @@
       <c r="Q10" s="1">
         <v>12</v>
       </c>
-      <c r="S10" s="10">
+      <c r="S10" s="9">
         <v>0</v>
       </c>
       <c r="T10" s="1">
@@ -3078,28 +3480,28 @@
       <c r="X10" s="1">
         <v>5</v>
       </c>
-      <c r="Z10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="10">
+      <c r="Z10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="9">
         <v>5</v>
       </c>
       <c r="AG10" s="1">
         <v>0</v>
       </c>
-      <c r="AH10" s="10">
+      <c r="AH10" s="9">
         <v>0</v>
       </c>
       <c r="AI10" s="1">
@@ -3115,7 +3517,7 @@
         <v>5</v>
       </c>
       <c r="AN10" s="2"/>
-      <c r="AO10" s="7"/>
+      <c r="AO10" s="6"/>
       <c r="AP10" s="2"/>
       <c r="AQ10" s="2"/>
       <c r="AR10" s="2"/>
@@ -3140,7 +3542,7 @@
       <c r="Q11" s="1">
         <v>7</v>
       </c>
-      <c r="S11" s="10">
+      <c r="S11" s="9">
         <v>0</v>
       </c>
       <c r="T11" s="1">
@@ -3179,7 +3581,7 @@
       <c r="AG11" s="1">
         <v>0</v>
       </c>
-      <c r="AH11" s="10">
+      <c r="AH11" s="9">
         <v>0</v>
       </c>
       <c r="AI11" s="1">
@@ -3195,7 +3597,7 @@
         <v>-5</v>
       </c>
       <c r="AN11" s="2"/>
-      <c r="AO11" s="7"/>
+      <c r="AO11" s="6"/>
       <c r="AP11" s="2"/>
       <c r="AQ11" s="2"/>
       <c r="AR11" s="2"/>
@@ -3220,7 +3622,7 @@
       <c r="Q12" s="1">
         <v>2</v>
       </c>
-      <c r="S12" s="10">
+      <c r="S12" s="9">
         <v>0</v>
       </c>
       <c r="T12" s="1">
@@ -3259,7 +3661,7 @@
       <c r="AG12" s="1">
         <v>0</v>
       </c>
-      <c r="AH12" s="10">
+      <c r="AH12" s="9">
         <v>0</v>
       </c>
       <c r="AI12" s="1">
@@ -3275,7 +3677,7 @@
         <v>-5</v>
       </c>
       <c r="AN12" s="2"/>
-      <c r="AO12" s="7"/>
+      <c r="AO12" s="6"/>
       <c r="AP12" s="2"/>
       <c r="AQ12" s="2"/>
       <c r="AR12" s="2"/>
@@ -3351,7 +3753,7 @@
       <c r="AJ14" s="1">
         <v>1</v>
       </c>
-      <c r="AK14" s="10">
+      <c r="AK14" s="9">
         <v>0</v>
       </c>
       <c r="AL14" s="1">
@@ -3426,7 +3828,7 @@
       <c r="AJ15" s="1">
         <v>0</v>
       </c>
-      <c r="AK15" s="10">
+      <c r="AK15" s="9">
         <v>0</v>
       </c>
       <c r="AL15" s="1">
@@ -3441,7 +3843,7 @@
       <c r="M16" s="1">
         <v>0</v>
       </c>
-      <c r="N16" s="9">
+      <c r="N16" s="8">
         <v>0</v>
       </c>
       <c r="O16" s="1">
@@ -3501,7 +3903,7 @@
       <c r="AJ16" s="1">
         <v>1</v>
       </c>
-      <c r="AK16" s="10">
+      <c r="AK16" s="9">
         <v>0</v>
       </c>
       <c r="AL16" s="1">
@@ -3516,7 +3918,7 @@
       <c r="M17" s="1">
         <v>0</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="9">
         <v>0</v>
       </c>
       <c r="O17" s="1">
@@ -3537,13 +3939,13 @@
       <c r="U17" s="1">
         <v>0</v>
       </c>
-      <c r="V17" s="10">
+      <c r="V17" s="9">
         <v>1</v>
       </c>
       <c r="W17" s="1">
         <v>0</v>
       </c>
-      <c r="X17" s="10">
+      <c r="X17" s="9">
         <v>5</v>
       </c>
       <c r="Z17" s="1">
@@ -3576,7 +3978,7 @@
       <c r="AJ17" s="1">
         <v>1</v>
       </c>
-      <c r="AK17" s="10">
+      <c r="AK17" s="9">
         <v>0</v>
       </c>
       <c r="AL17" s="1">
@@ -3591,7 +3993,7 @@
       <c r="M18" s="1">
         <v>0</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="9">
         <v>0</v>
       </c>
       <c r="O18" s="1">
@@ -3630,7 +4032,7 @@
       <c r="AB18" s="1">
         <v>0</v>
       </c>
-      <c r="AC18" s="10">
+      <c r="AC18" s="9">
         <v>0</v>
       </c>
       <c r="AD18" s="1">
@@ -3648,7 +4050,7 @@
       <c r="AI18" s="1">
         <v>0</v>
       </c>
-      <c r="AJ18" s="11">
+      <c r="AJ18" s="1">
         <v>0</v>
       </c>
       <c r="AK18" s="1">
@@ -3672,10 +4074,10 @@
       <c r="N20" s="1">
         <v>1</v>
       </c>
-      <c r="O20" s="10">
-        <v>0</v>
-      </c>
-      <c r="P20" s="11">
+      <c r="O20" s="9">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
         <v>0</v>
       </c>
       <c r="Q20" s="1">
@@ -3684,16 +4086,16 @@
       <c r="S20" s="1">
         <v>1</v>
       </c>
-      <c r="T20" s="10">
-        <v>0</v>
-      </c>
-      <c r="U20" s="11">
-        <v>1</v>
-      </c>
-      <c r="V20" s="11">
-        <v>0</v>
-      </c>
-      <c r="W20" s="11">
+      <c r="T20" s="9">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1">
+        <v>1</v>
+      </c>
+      <c r="V20" s="1">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1">
         <v>0</v>
       </c>
       <c r="X20" s="1">
@@ -3705,16 +4107,16 @@
       <c r="AA20" s="1">
         <v>0</v>
       </c>
-      <c r="AB20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="12">
+      <c r="AB20" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="10">
         <v>2</v>
       </c>
       <c r="AG20" s="1">
@@ -3735,10 +4137,10 @@
       <c r="N21" s="1">
         <v>-1</v>
       </c>
-      <c r="O21" s="10">
-        <v>0</v>
-      </c>
-      <c r="P21" s="11">
+      <c r="O21" s="9">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
         <v>0</v>
       </c>
       <c r="Q21" s="1">
@@ -3750,13 +4152,13 @@
       <c r="T21" s="1">
         <v>1</v>
       </c>
-      <c r="U21" s="11">
+      <c r="U21" s="1">
         <v>-1</v>
       </c>
-      <c r="V21" s="11">
-        <v>0</v>
-      </c>
-      <c r="W21" s="11">
+      <c r="V21" s="1">
+        <v>0</v>
+      </c>
+      <c r="W21" s="1">
         <v>0</v>
       </c>
       <c r="X21" s="1">
@@ -3768,16 +4170,16 @@
       <c r="AA21" s="1">
         <v>1</v>
       </c>
-      <c r="AB21" s="12">
+      <c r="AB21" s="10">
         <v>-1</v>
       </c>
-      <c r="AC21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="12">
+      <c r="AC21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="10">
         <v>5</v>
       </c>
       <c r="AG21" s="1">
@@ -3798,10 +4200,10 @@
       <c r="N22" s="1">
         <v>0</v>
       </c>
-      <c r="O22" s="10">
-        <v>0</v>
-      </c>
-      <c r="P22" s="11">
+      <c r="O22" s="9">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
         <v>0</v>
       </c>
       <c r="Q22" s="1">
@@ -3816,10 +4218,10 @@
       <c r="U22" s="1">
         <v>0</v>
       </c>
-      <c r="V22" s="11">
-        <v>0</v>
-      </c>
-      <c r="W22" s="11">
+      <c r="V22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1">
         <v>0</v>
       </c>
       <c r="X22" s="1">
@@ -3834,13 +4236,13 @@
       <c r="AB22" s="1">
         <v>0</v>
       </c>
-      <c r="AC22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="12">
+      <c r="AC22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="10">
         <v>0</v>
       </c>
       <c r="AG22" s="1">
@@ -3864,7 +4266,7 @@
       <c r="O23" s="1">
         <v>1</v>
       </c>
-      <c r="P23" s="11">
+      <c r="P23" s="1">
         <v>0</v>
       </c>
       <c r="Q23" s="1">
@@ -3882,7 +4284,7 @@
       <c r="V23" s="1">
         <v>1</v>
       </c>
-      <c r="W23" s="11">
+      <c r="W23" s="1">
         <v>0</v>
       </c>
       <c r="X23" s="1">
@@ -3900,10 +4302,10 @@
       <c r="AC23" s="1">
         <v>1</v>
       </c>
-      <c r="AD23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="12">
+      <c r="AD23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="10">
         <v>5</v>
       </c>
       <c r="AG23" s="1">
@@ -3924,7 +4326,7 @@
       <c r="N24" s="1">
         <v>0</v>
       </c>
-      <c r="O24" s="11">
+      <c r="O24" s="1">
         <v>0</v>
       </c>
       <c r="P24" s="1">
@@ -3942,7 +4344,7 @@
       <c r="U24" s="1">
         <v>0</v>
       </c>
-      <c r="V24" s="11">
+      <c r="V24" s="1">
         <v>0</v>
       </c>
       <c r="W24" s="1">
@@ -3960,13 +4362,13 @@
       <c r="AB24" s="1">
         <v>0</v>
       </c>
-      <c r="AC24" s="11">
+      <c r="AC24" s="1">
         <v>0</v>
       </c>
       <c r="AD24" s="1">
         <v>1</v>
       </c>
-      <c r="AE24" s="12">
+      <c r="AE24" s="10">
         <v>0</v>
       </c>
       <c r="AG24" s="1">
@@ -5436,23 +5838,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{933C748A-F57E-419A-A335-7369B2990447}">
-  <dimension ref="B1:AS496"/>
+  <dimension ref="B1:AR496"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="36" width="4.28515625" customWidth="1"/>
     <col min="37" max="37" width="4.42578125" customWidth="1"/>
-    <col min="38" max="40" width="4.28515625" customWidth="1"/>
-    <col min="41" max="41" width="13" customWidth="1"/>
-    <col min="42" max="89" width="4.28515625" customWidth="1"/>
+    <col min="38" max="88" width="4.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
       <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
@@ -5470,9 +5870,8 @@
       <c r="AP1" s="2"/>
       <c r="AQ1" s="2"/>
       <c r="AR1" s="2"/>
-      <c r="AS1" s="2"/>
-    </row>
-    <row r="2" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1">
         <v>1</v>
       </c>
@@ -5489,6 +5888,25 @@
         <v>6</v>
       </c>
       <c r="I2" s="1">
+        <v>10</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>4</v>
+      </c>
+      <c r="T2" s="1" cm="1">
+        <f t="array" ref="T2:T7">MMULT(M2:P7,R2:R5)</f>
         <v>10</v>
       </c>
       <c r="AN2" s="2"/>
@@ -5496,9 +5914,8 @@
       <c r="AP2" s="2"/>
       <c r="AQ2" s="2"/>
       <c r="AR2" s="2"/>
-      <c r="AS2" s="2"/>
-    </row>
-    <row r="3" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -5515,6 +5932,24 @@
         <v>7</v>
       </c>
       <c r="I3" s="1">
+        <v>11</v>
+      </c>
+      <c r="M3" s="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1">
+        <v>1</v>
+      </c>
+      <c r="T3" s="1">
         <v>11</v>
       </c>
       <c r="AN3" s="2"/>
@@ -5522,9 +5957,8 @@
       <c r="AP3" s="2"/>
       <c r="AQ3" s="2"/>
       <c r="AR3" s="2"/>
-      <c r="AS3" s="2"/>
-    </row>
-    <row r="4" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -5541,6 +5975,24 @@
         <v>8</v>
       </c>
       <c r="I4" s="1">
+        <v>11</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
+      <c r="R4" s="1">
+        <v>5</v>
+      </c>
+      <c r="T4" s="1">
         <v>11</v>
       </c>
       <c r="AN4" s="2"/>
@@ -5548,9 +6000,8 @@
       <c r="AP4" s="2"/>
       <c r="AQ4" s="2"/>
       <c r="AR4" s="2"/>
-      <c r="AS4" s="2"/>
-    </row>
-    <row r="5" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -5575,8 +6026,26 @@
       <c r="I5" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>2</v>
+      </c>
+      <c r="T5" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>1</v>
       </c>
@@ -5592,9 +6061,23 @@
       <c r="I6" s="1">
         <v>10</v>
       </c>
-      <c r="AO6" s="3"/>
-    </row>
-    <row r="7" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1">
+        <v>1</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>0</v>
       </c>
@@ -5610,9 +6093,23 @@
       <c r="I7" s="1">
         <v>5</v>
       </c>
-      <c r="AO7" s="3"/>
-    </row>
-    <row r="8" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>0</v>
       </c>
@@ -5625,36 +6122,1183 @@
       <c r="E8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AO8" s="3"/>
-    </row>
-    <row r="9" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AO9" s="3"/>
-    </row>
-    <row r="10" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AO10" s="3"/>
-    </row>
-    <row r="11" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:45" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="9" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1">
+        <f>MDETERM(B12:G17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>1</v>
+      </c>
+      <c r="R12" s="1">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <v>1</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0</v>
+      </c>
+      <c r="V13" s="1">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1">
+        <v>1</v>
+      </c>
+      <c r="U14" s="1">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>-1</v>
+      </c>
+      <c r="T15" s="1">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
+        <v>-5</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:44" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>1</v>
+      </c>
+      <c r="T17" s="1">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AJ18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AK18" s="1">
+        <v>-2</v>
+      </c>
+      <c r="AL18" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AM18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>10</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>10</v>
+      </c>
+      <c r="R19" s="1">
+        <v>1</v>
+      </c>
+      <c r="S19" s="1">
+        <v>1</v>
+      </c>
+      <c r="T19" s="1">
+        <v>1</v>
+      </c>
+      <c r="U19" s="1">
+        <v>0</v>
+      </c>
+      <c r="V19" s="1">
+        <v>0</v>
+      </c>
+      <c r="W19" s="1">
+        <v>0</v>
+      </c>
+      <c r="X19" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="1">
+        <v>6</v>
+      </c>
+      <c r="AH19" s="1">
+        <v>6</v>
+      </c>
+      <c r="AI19" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AK19" s="1">
+        <v>8</v>
+      </c>
+      <c r="AL19" s="1">
+        <v>7</v>
+      </c>
+      <c r="AM19" s="1">
+        <v>6</v>
+      </c>
+      <c r="AN19" s="1">
+        <v>5</v>
+      </c>
+      <c r="AO19" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
+        <v>1</v>
+      </c>
+      <c r="T20" s="1">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="V20" s="1">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AH20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AI20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="1">
+        <v>-3</v>
+      </c>
+      <c r="AL20" s="1">
+        <v>-2</v>
+      </c>
+      <c r="AM20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AN20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>5</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1">
+        <v>1</v>
+      </c>
+      <c r="U21" s="1">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
+        <v>0</v>
+      </c>
+      <c r="W21" s="1">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="1">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="1">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="1">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="1">
+        <v>5</v>
+      </c>
+      <c r="AM21" s="1">
+        <v>5</v>
+      </c>
+      <c r="AN21" s="1">
+        <v>5</v>
+      </c>
+      <c r="AO21" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>-5</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>-1</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>-5</v>
+      </c>
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1">
+        <v>0</v>
+      </c>
+      <c r="X22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AK22" s="1">
+        <v>-2</v>
+      </c>
+      <c r="AL22" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AM22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AO22" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
+      <c r="T23" s="1">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1">
+        <v>0</v>
+      </c>
+      <c r="V23" s="1">
+        <v>0</v>
+      </c>
+      <c r="W23" s="1">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="1">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>0</v>
+      </c>
+      <c r="R24" s="1">
+        <v>0</v>
+      </c>
+      <c r="S24" s="1">
+        <v>0</v>
+      </c>
+      <c r="T24" s="1">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1">
+        <v>0</v>
+      </c>
+      <c r="V24" s="1">
+        <v>0</v>
+      </c>
+      <c r="W24" s="1">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Day10/matrixes.xlsx
+++ b/Day10/matrixes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e03748fe74b2749e/Projetos/AdventOfCode2025/AdventOfCode2025/Day10/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1013" documentId="8_{804FC923-46C6-45E0-983F-7CE295EDADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D8F45AE-9725-4DA9-AF1F-13949E4F5E97}"/>
+  <xr:revisionPtr revIDLastSave="1034" documentId="8_{804FC923-46C6-45E0-983F-7CE295EDADD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75A9189C-6015-4D63-BA73-D9F0E2E83A01}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E1441335-4A8F-4FC7-82E1-14FF11680EDB}"/>
   </bookViews>
@@ -1999,6 +1999,27 @@
       <c r="W10" s="1">
         <v>7</v>
       </c>
+      <c r="Y10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>7</v>
+      </c>
       <c r="AO10" s="3"/>
     </row>
     <row r="11" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2062,6 +2083,27 @@
       <c r="W11" s="1">
         <v>5</v>
       </c>
+      <c r="Y11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
@@ -2124,6 +2166,27 @@
       <c r="W12" s="1">
         <v>4</v>
       </c>
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
@@ -2186,6 +2249,27 @@
       <c r="W13" s="1">
         <v>3</v>
       </c>
+      <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
@@ -2248,6 +2332,27 @@
       <c r="W14" s="1">
         <v>0</v>
       </c>
+      <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="2:41" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
@@ -2308,6 +2413,27 @@
         <v>0</v>
       </c>
       <c r="W15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="1">
         <v>0</v>
       </c>
     </row>
